--- a/Proyecto/PREGAME/2.PRIMERA INTERACION/SPRINT1 V.3.xlsx
+++ b/Proyecto/PREGAME/2.PRIMERA INTERACION/SPRINT1 V.3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F057400-B62B-46D9-8C06-9FC1D0137D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF50AB0F-C55B-4128-B083-AA2420701042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="109">
   <si>
     <t>ID</t>
   </si>
@@ -229,9 +229,6 @@
   </si>
   <si>
     <t>Realizar las respectivas pruebas para comprobar el buen funcionamiento de la tarea</t>
-  </si>
-  <si>
-    <t>REQ002-5</t>
   </si>
   <si>
     <t>#intentos de ingreso</t>
@@ -690,25 +687,25 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -782,28 +779,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>37</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>36</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>29</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -848,25 +845,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>37</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>31.714285714285715</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>26.428571428571431</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>21.142857142857146</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15.857142857142861</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10.571428571428577</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.2857142857142918</c:v>
+                  <c:v>5.0000000000000009</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -1367,7 +1364,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G2" s="21" t="s">
         <v>13</v>
@@ -1393,7 +1390,7 @@
         <v>22</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G3" s="21" t="s">
         <v>13</v>
@@ -1419,7 +1416,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G4" s="21" t="s">
         <v>13</v>
@@ -1445,7 +1442,7 @@
         <v>26</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G5" s="21" t="s">
         <v>27</v>
@@ -1471,7 +1468,7 @@
         <v>31</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G6" s="21" t="s">
         <v>27</v>
@@ -2524,7 +2521,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>10</v>
@@ -2547,12 +2544,12 @@
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="32"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="44"/>
       <c r="G5" s="3" t="s">
         <v>41</v>
       </c>
@@ -2565,14 +2562,14 @@
       <c r="B6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="32"/>
+      <c r="C6" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="44"/>
       <c r="G6" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="17">
@@ -2583,14 +2580,14 @@
       <c r="B7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="32"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="44"/>
       <c r="G7" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="17">
@@ -2601,14 +2598,14 @@
       <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="44"/>
       <c r="G8" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="18">
@@ -2619,14 +2616,14 @@
       <c r="B9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="44"/>
       <c r="G9" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="17">
@@ -2638,7 +2635,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>10</v>
@@ -2650,24 +2647,24 @@
         <v>22</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>13</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="44"/>
       <c r="G11" s="3" t="s">
         <v>41</v>
       </c>
@@ -2697,14 +2694,14 @@
       <c r="B12" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="39"/>
+      <c r="C12" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="41"/>
       <c r="G12" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1">
@@ -2715,14 +2712,14 @@
       <c r="B13" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="39"/>
+      <c r="C13" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="41"/>
       <c r="G13" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1">
@@ -2733,14 +2730,14 @@
       <c r="B14" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="39"/>
+      <c r="C14" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="41"/>
       <c r="G14" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1">
@@ -2751,14 +2748,14 @@
       <c r="B15" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="39"/>
+      <c r="C15" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="41"/>
       <c r="G15" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1">
@@ -2770,7 +2767,7 @@
         <v>19</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>10</v>
@@ -2791,12 +2788,12 @@
     </row>
     <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="32"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="44"/>
       <c r="G17" s="3" t="s">
         <v>41</v>
       </c>
@@ -2807,16 +2804,16 @@
     </row>
     <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35"/>
+        <v>60</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="38"/>
       <c r="G18" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1">
@@ -2825,16 +2822,16 @@
     </row>
     <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="35"/>
+        <v>63</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="38"/>
       <c r="G19" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1">
@@ -2843,16 +2840,16 @@
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="35"/>
+        <v>65</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="38"/>
       <c r="G20" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1">
@@ -2861,16 +2858,16 @@
     </row>
     <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="39"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41"/>
       <c r="G21" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1">
@@ -2882,7 +2879,7 @@
         <v>23</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>10</v>
@@ -2894,24 +2891,24 @@
         <v>26</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>13</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="32"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="44"/>
       <c r="G23" s="3" t="s">
         <v>41</v>
       </c>
@@ -2939,14 +2936,14 @@
     </row>
     <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="35"/>
+        <v>69</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="38"/>
       <c r="G24" s="4" t="s">
         <v>44</v>
       </c>
@@ -2957,14 +2954,14 @@
     </row>
     <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="39"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="41"/>
       <c r="G25" s="4" t="s">
         <v>44</v>
       </c>
@@ -2975,14 +2972,14 @@
     </row>
     <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="39"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="4" t="s">
         <v>44</v>
       </c>
@@ -2996,7 +2993,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>10</v>
@@ -3008,24 +3005,24 @@
         <v>31</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="32"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="44"/>
       <c r="G28" s="3" t="s">
         <v>41</v>
       </c>
@@ -3053,16 +3050,16 @@
     </row>
     <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="43"/>
+        <v>75</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="32"/>
       <c r="G29" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="1">
@@ -3071,16 +3068,16 @@
     </row>
     <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="43"/>
+        <v>77</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="32"/>
       <c r="G30" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H30" s="4"/>
       <c r="I30" s="1">
@@ -3089,16 +3086,16 @@
     </row>
     <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="46"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="35"/>
       <c r="G31" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H31" s="4"/>
       <c r="I31" s="1">
@@ -3107,16 +3104,16 @@
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="C32" s="44" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="46"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="35"/>
       <c r="G32" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H32" s="4"/>
       <c r="I32" s="1">
@@ -4063,15 +4060,6 @@
     <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C28:F28"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C11:F11"/>
@@ -4087,6 +4075,15 @@
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C28:F28"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -4117,28 +4114,28 @@
         <v>42</v>
       </c>
       <c r="D3" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="K3" s="10" t="s">
         <v>89</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4203,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="13">
-        <f t="shared" ref="K5:K23" si="0">SUM(D5:J5)</f>
+        <f t="shared" ref="K5:K22" si="0">SUM(D5:J5)</f>
         <v>2</v>
       </c>
     </row>
@@ -4409,7 +4406,7 @@
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C12" s="12">
         <v>2</v>
@@ -4421,9 +4418,9 @@
         <v>0</v>
       </c>
       <c r="F12" s="11">
-        <v>3</v>
-      </c>
-      <c r="G12" s="11">
+        <v>0</v>
+      </c>
+      <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" s="11">
@@ -4437,15 +4434,15 @@
       </c>
       <c r="K12" s="13">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C13" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="11">
         <v>0</v>
@@ -4457,7 +4454,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" s="11">
         <v>0</v>
@@ -4470,15 +4467,15 @@
       </c>
       <c r="K13" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="11">
         <v>0</v>
@@ -4508,7 +4505,7 @@
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" s="12">
         <v>2</v>
@@ -4541,7 +4538,7 @@
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" s="12">
         <v>2</v>
@@ -4552,11 +4549,11 @@
       <c r="E16" s="11">
         <v>0</v>
       </c>
-      <c r="F16" s="11">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" s="11">
+        <v>0</v>
       </c>
       <c r="H16" s="11">
         <v>0</v>
@@ -4569,12 +4566,12 @@
       </c>
       <c r="K16" s="13">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" s="12">
         <v>2</v>
@@ -4592,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17" s="11">
         <v>0</v>
@@ -4602,12 +4599,12 @@
       </c>
       <c r="K17" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C18" s="12">
         <v>2</v>
@@ -4625,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" s="11">
         <v>0</v>
@@ -4635,12 +4632,12 @@
       </c>
       <c r="K18" s="13">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" s="12">
         <v>2</v>
@@ -4648,7 +4645,7 @@
       <c r="D19" s="11">
         <v>0</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
@@ -4658,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" s="11">
         <v>0</v>
@@ -4668,15 +4665,15 @@
       </c>
       <c r="K19" s="13">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C20" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="11">
         <v>0</v>
@@ -4694,14 +4691,14 @@
         <v>0</v>
       </c>
       <c r="I20" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="11">
         <v>0</v>
       </c>
       <c r="K20" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4709,7 +4706,7 @@
         <v>78</v>
       </c>
       <c r="C21" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="11">
         <v>0</v>
@@ -4739,7 +4736,7 @@
     </row>
     <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C22" s="12">
         <v>2</v>
@@ -4770,112 +4767,80 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" s="12">
-        <v>2</v>
-      </c>
-      <c r="D23" s="11">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23" s="11">
-        <v>0</v>
-      </c>
-      <c r="H23" s="11">
-        <v>0</v>
-      </c>
-      <c r="I23" s="11">
-        <v>2</v>
-      </c>
-      <c r="J23" s="11">
-        <v>0</v>
-      </c>
-      <c r="K23" s="13">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
+    <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C26" s="15">
-        <f>SUM(C4:C23)</f>
-        <v>37</v>
+        <f>SUM(C4:C22)</f>
+        <v>35</v>
       </c>
       <c r="D26" s="15">
-        <f t="shared" ref="D26:J26" si="1">C26-SUM(D4:D23)</f>
-        <v>36</v>
+        <f>C26-SUM(D4:D22)</f>
+        <v>34</v>
       </c>
       <c r="E26" s="16">
-        <f t="shared" si="1"/>
-        <v>29</v>
+        <f>D26-SUM(E4:E22)</f>
+        <v>27</v>
       </c>
       <c r="F26" s="15">
-        <f t="shared" si="1"/>
-        <v>19</v>
+        <f>E26-SUM(F4:F22)</f>
+        <v>20</v>
       </c>
       <c r="G26" s="15">
-        <f t="shared" si="1"/>
-        <v>13</v>
+        <f>F26-SUM(G4:G22)</f>
+        <v>14</v>
       </c>
       <c r="H26" s="15">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <f>G26-SUM(H4:H22)</f>
+        <v>9</v>
       </c>
       <c r="I26" s="15">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>H26-SUM(I4:I22)</f>
+        <v>3</v>
       </c>
       <c r="J26" s="15">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>I26-SUM(J4:J22)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C27" s="15">
-        <f>SUM(C4:C23)</f>
-        <v>37</v>
+        <f>SUM(C4:C22)</f>
+        <v>35</v>
       </c>
       <c r="D27" s="15">
-        <f>C27-(SUM(C4:C23)/7)</f>
-        <v>31.714285714285715</v>
+        <f>C27-(SUM(C4:C22)/7)</f>
+        <v>30</v>
       </c>
       <c r="E27" s="16">
-        <f>D27-(SUM(C4:C23)/7)</f>
-        <v>26.428571428571431</v>
+        <f>D27-(SUM(C4:C22)/7)</f>
+        <v>25</v>
       </c>
       <c r="F27" s="15">
-        <f>E27-(SUM(C4:C23)/7)</f>
-        <v>21.142857142857146</v>
+        <f>E27-(SUM(C4:C22)/7)</f>
+        <v>20</v>
       </c>
       <c r="G27" s="15" cm="1">
-        <f t="array" ref="G27">F27-(SUM(C4:C23/7))</f>
-        <v>15.857142857142861</v>
+        <f t="array" ref="G27">F27-(SUM(C4:C22/7))</f>
+        <v>15</v>
       </c>
       <c r="H27" s="15" cm="1">
-        <f t="array" ref="H27">G27-(SUM(C4:C23/7))</f>
-        <v>10.571428571428577</v>
+        <f t="array" ref="H27">G27-(SUM(C4:C22/7))</f>
+        <v>10</v>
       </c>
       <c r="I27" s="15" cm="1">
-        <f t="array" ref="I27">H27-(SUM(C4:C23/7))</f>
-        <v>5.2857142857142918</v>
+        <f t="array" ref="I27">H27-(SUM(C4:C22/7))</f>
+        <v>5.0000000000000009</v>
       </c>
       <c r="J27" s="15">
-        <f>I27-(SUM(C4:C23)/7)</f>
+        <f>I27-(SUM(C4:C22)/7)</f>
         <v>0</v>
       </c>
     </row>
